--- a/Input/Cigna_Global_Health/cignaScript/inputRates/benefits.xlsx
+++ b/Input/Cigna_Global_Health/cignaScript/inputRates/benefits.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="186">
   <si>
     <t xml:space="preserve">PlanName</t>
   </si>
@@ -200,6 +200,18 @@
   </si>
   <si>
     <t xml:space="preserve">discounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discounts1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discounts2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discounts3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">discounts4</t>
   </si>
   <si>
     <t xml:space="preserve">Platinum</t>
@@ -558,6 +570,18 @@
   </si>
   <si>
     <t xml:space="preserve">discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseDiscount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dentalDiscount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wellnessDiscount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maternityDiscount</t>
   </si>
   <si>
     <t xml:space="preserve">Silver</t>
@@ -997,24 +1021,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BJ50"/>
-  <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BN50"/>
+  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="3" style="0" width="11.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="15" style="1" width="11.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="22" style="0" width="11.72"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="45" min="45" style="2" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="2" width="11.52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="82.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="77.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="23.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="50" style="0" width="11.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="36.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="24.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="3" width="63.17"/>
@@ -1022,9 +1041,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="3" width="64.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="3" width="63.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="3" width="61.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="11.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="72.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="62" style="0" width="11.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="44.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1210,45 +1227,59 @@
       <c r="BJ1" s="0" t="s">
         <v>59</v>
       </c>
+      <c r="BK1" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="BL1" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="BM1" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="BN1" s="0" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="441.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E2" s="8"/>
       <c r="F2" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="M2" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O2" s="6" t="s">
         <v>53</v>
@@ -1273,152 +1304,166 @@
       </c>
       <c r="V2" s="8"/>
       <c r="W2" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Z2" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="AA2" s="8"/>
       <c r="AB2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AD2" s="8"/>
       <c r="AE2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AF2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AJ2" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK2" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL2" s="8"/>
       <c r="AM2" s="8"/>
       <c r="AN2" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AO2" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AP2" s="8"/>
       <c r="AQ2" s="8"/>
       <c r="AR2" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AS2" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AT2" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AU2" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="AV2" s="0" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="AW2" s="0" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="AX2" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AY2" s="12" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="AZ2" s="0" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="BA2" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="BB2" s="0" t="s">
         <v>27</v>
       </c>
       <c r="BC2" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="BD2" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="BE2" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="BF2" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="BG2" s="13" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="BH2" s="0" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="BI2" s="0" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="BJ2" s="0" t="s">
-        <v>93</v>
+        <v>97</v>
+      </c>
+      <c r="BK2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="BL2" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="BM2" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="BN2" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E3" s="8"/>
       <c r="F3" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="8"/>
+        <v>104</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="M3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O3" s="6" t="s">
         <v>53</v>
@@ -1443,122 +1488,124 @@
       </c>
       <c r="V3" s="8"/>
       <c r="W3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="AA3" s="8"/>
       <c r="AB3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AD3" s="8"/>
       <c r="AE3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL3" s="8"/>
       <c r="AM3" s="8"/>
       <c r="AN3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AO3" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AP3" s="8"/>
       <c r="AQ3" s="8"/>
       <c r="AR3" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AS3" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AT3" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AU3" s="10" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="AV3" s="0" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="BA3" s="8" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="BB3" s="0" t="s">
         <v>30</v>
       </c>
       <c r="BH3" s="0" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="BI3" s="14" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="L4" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="M4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O4" s="6" t="s">
         <v>53</v>
@@ -1583,84 +1630,84 @@
       </c>
       <c r="V4" s="8"/>
       <c r="W4" s="4" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="AA4" s="8"/>
       <c r="AB4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AD4" s="8"/>
       <c r="AE4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AJ4" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="AK4" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="8"/>
       <c r="AM4" s="8"/>
       <c r="AN4" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AO4" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AP4" s="8"/>
       <c r="AQ4" s="8"/>
       <c r="AR4" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AS4" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AT4" s="9" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AU4" s="10" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="AV4" s="0" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="BB4" s="0" t="s">
         <v>35</v>
       </c>
       <c r="BI4" s="14" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU5" s="10" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="AV5" s="0" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="BB5" s="8" t="s">
         <v>31</v>
@@ -1672,10 +1719,10 @@
       <c r="Q6" s="6"/>
       <c r="R6" s="15"/>
       <c r="AU6" s="10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="AV6" s="0" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="BB6" s="0" t="s">
         <v>28</v>
@@ -1683,10 +1730,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU7" s="10" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="AV7" s="0" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="BB7" s="14" t="s">
         <v>34</v>
@@ -1694,259 +1741,259 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU8" s="10" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="AV8" s="0" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU9" s="10" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="AV9" s="0" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU10" s="10" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="AV10" s="0" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU11" s="10" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="AV11" s="0" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU12" s="10" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="AV12" s="0" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU13" s="10" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="AV13" s="0" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU14" s="10" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AV14" s="0" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU15" s="10" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="AV15" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU16" s="10" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="AV16" s="0" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU17" s="10" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="AV17" s="0" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU18" s="10" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="AV18" s="0" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU19" s="10" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AV19" s="0" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU20" s="10" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AV20" s="0" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU21" s="10" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="AV21" s="0" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU22" s="10" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU23" s="10" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU24" s="10" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU25" s="10" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU26" s="10" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU27" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU28" s="10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU29" s="10" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU30" s="10" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU31" s="10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU32" s="10" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU33" s="10" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU34" s="10" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU35" s="10" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU36" s="10" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU37" s="10" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU38" s="10" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU39" s="10" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU40" s="10" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU41" s="10" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU42" s="10" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU43" s="10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU44" s="10" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU45" s="10" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU46" s="10" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU47" s="10" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU48" s="10" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU49" s="10" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AU50" s="10" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/Input/Cigna_Global_Health/cignaScript/inputRates/benefits.xlsx
+++ b/Input/Cigna_Global_Health/cignaScript/inputRates/benefits.xlsx
@@ -656,184 +656,184 @@
     <t xml:space="preserve">$0, 20% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
+    <t xml:space="preserve">$150, 0% Co-insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0, 30% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$150, 10% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0, 30% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$150, 20% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 0% Co-insurance, $0 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$150, 30% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 10% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500, 0% Co-insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 10% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500, 10% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 20% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500, 20% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 20% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$500, 30% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$375, 30% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
     <t xml:space="preserve">$1,000, 0% Co-insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">$0, 30% Co-insurance, $2,000 Out of pocket</t>
+    <t xml:space="preserve">$375, 30% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
     <t xml:space="preserve">$1,000, 10% Co-insurance, $3,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$0, 30% Co-insurance, $5,000 Out of pocket</t>
+    <t xml:space="preserve">$750, 0% Co-insurance, $0 Out of pocket</t>
   </si>
   <si>
     <t xml:space="preserve">$1,000, 20% Co-insurance, $3,000 Out of pocket</t>
   </si>
   <si>
+    <t xml:space="preserve">$750, 10% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,000, 30% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$750, 10% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,500, 0% Co-insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$750, 20% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,500, 10% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$750, 20% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,500, 20% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$750, 30% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,500, 30% Co-insurance, $3,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$750, 30% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
     <t xml:space="preserve">$1,500, 0% Co-insurance, $0 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,000, 30% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 10% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,500, 0% Co-insurance</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 10% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,500, 10% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 20% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,500, 20% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 20% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$1,500, 30% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 30% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$150, 0% Co-insurance</t>
-  </si>
-  <si>
     <t xml:space="preserve">$1,500, 30% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$150, 10% Co-insurance, $3,000 Out of pocket</t>
+    <t xml:space="preserve">$3,000, 0% Co-insurance, $0 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 10% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 10% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 20% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 20% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 30% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3,000, 30% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 0% Co-insurance, $0 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 10% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 10% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 20% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 20% Co-insurance, $5,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 30% Co-insurance, $2,000 Out of pocket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$7,500, 30% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
     <t xml:space="preserve">$10,000, 0% Co-insurance, $0 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$150, 20% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 10% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$150, 30% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 10% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$500, 0% Co-insurance</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 20% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$500, 10% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 20% Co-insurance, $5,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$500, 20% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 30% Co-insurance, $2,000 Out of pocket</t>
   </si>
   <si>
-    <t xml:space="preserve">$500, 30% Co-insurance, $3,000 Out of pocket</t>
-  </si>
-  <si>
     <t xml:space="preserve">$10,000, 30% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 0% Co-insurance, $0 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 10% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 10% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 20% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 20% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 30% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$3,000, 30% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 0% Co-insurance, $0 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 10% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 10% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 20% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 20% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 30% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$375, 30% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 0% Co-insurance, $0 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 10% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 10% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 20% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 20% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 30% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$7,500, 30% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 0% Co-insurance, $0 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 10% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 10% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 20% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 20% Co-insurance, $5,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 30% Co-insurance, $2,000 Out of pocket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$750, 30% Co-insurance, $5,000 Out of pocket</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1026,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:BN50"/>
-  <sheetFormatPr defaultColWidth="11.7578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="15" style="1" width="11.67"/>
@@ -1424,7 +1424,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="55.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>102</v>
       </c>
@@ -1566,7 +1566,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="55.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
         <v>113</v>
       </c>
